--- a/resources/templates/standard/A2200-02.xlsx
+++ b/resources/templates/standard/A2200-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="79">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>(           )년 경영검토 계획서</t>
   </si>
@@ -819,12 +822,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -854,30 +859,30 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4"/>
       <c r="AN1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -938,7 +943,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -954,7 +959,7 @@
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
@@ -1038,7 +1043,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1052,7 +1057,7 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -1104,69 +1109,69 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
       <c r="P6" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
       <c r="V6" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
       <c r="Y6" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC6" s="10"/>
       <c r="AD6" s="10"/>
       <c r="AE6" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF6" s="10"/>
       <c r="AG6" s="10"/>
       <c r="AH6" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI6" s="10"/>
       <c r="AJ6" s="10"/>
       <c r="AK6" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL6" s="10"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO6" s="10"/>
       <c r="AP6" s="10"/>
       <c r="AQ6" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR6" s="10"/>
       <c r="AS6" s="10"/>
       <c r="AT6" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU6" s="10"/>
       <c r="AV6" s="10"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1177,7 +1182,7 @@
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
@@ -1229,7 +1234,7 @@
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -1272,7 +1277,7 @@
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -1324,11 +1329,11 @@
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
@@ -1339,7 +1344,7 @@
       <c r="J10" s="16"/>
       <c r="K10" s="16"/>
       <c r="L10" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
@@ -1350,17 +1355,17 @@
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="U10" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V10" s="16"/>
       <c r="W10" s="16"/>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB10" s="16"/>
       <c r="AC10" s="16"/>
@@ -1371,7 +1376,7 @@
       <c r="AH10" s="16"/>
       <c r="AI10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK10" s="16"/>
       <c r="AL10" s="16"/>
@@ -1382,7 +1387,7 @@
       <c r="AQ10" s="16"/>
       <c r="AR10" s="16"/>
       <c r="AS10" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AT10" s="16"/>
       <c r="AU10" s="16"/>
@@ -1394,7 +1399,7 @@
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
@@ -1405,7 +1410,7 @@
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
       <c r="L11" s="18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
@@ -1416,7 +1421,7 @@
       <c r="S11" s="18"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V11" s="18"/>
       <c r="W11" s="18"/>
@@ -1426,7 +1431,7 @@
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB11" s="18"/>
       <c r="AC11" s="18"/>
@@ -1437,7 +1442,7 @@
       <c r="AH11" s="18"/>
       <c r="AI11" s="18"/>
       <c r="AJ11" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AK11" s="18"/>
       <c r="AL11" s="18"/>
@@ -1448,7 +1453,7 @@
       <c r="AQ11" s="18"/>
       <c r="AR11" s="18"/>
       <c r="AS11" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AT11" s="18"/>
       <c r="AU11" s="18"/>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
@@ -1471,7 +1476,7 @@
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
@@ -1482,7 +1487,7 @@
       <c r="S12" s="17"/>
       <c r="T12" s="17"/>
       <c r="U12" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V12" s="17"/>
       <c r="W12" s="17"/>
@@ -1492,7 +1497,7 @@
       </c>
       <c r="Z12" s="16"/>
       <c r="AA12" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AB12" s="18"/>
       <c r="AC12" s="18"/>
@@ -1503,7 +1508,7 @@
       <c r="AH12" s="18"/>
       <c r="AI12" s="18"/>
       <c r="AJ12" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AK12" s="17"/>
       <c r="AL12" s="17"/>
@@ -1514,7 +1519,7 @@
       <c r="AQ12" s="17"/>
       <c r="AR12" s="17"/>
       <c r="AS12" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AT12" s="18"/>
       <c r="AU12" s="18"/>
@@ -1526,7 +1531,7 @@
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
@@ -1537,7 +1542,7 @@
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
       <c r="L13" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
@@ -1548,7 +1553,7 @@
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V13" s="18"/>
       <c r="W13" s="18"/>
@@ -1558,7 +1563,7 @@
       </c>
       <c r="Z13" s="16"/>
       <c r="AA13" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB13" s="17"/>
       <c r="AC13" s="17"/>
@@ -1569,7 +1574,7 @@
       <c r="AH13" s="17"/>
       <c r="AI13" s="17"/>
       <c r="AJ13" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK13" s="17"/>
       <c r="AL13" s="17"/>
@@ -1580,7 +1585,7 @@
       <c r="AQ13" s="17"/>
       <c r="AR13" s="17"/>
       <c r="AS13" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AT13" s="18"/>
       <c r="AU13" s="18"/>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
@@ -1603,7 +1608,7 @@
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
       <c r="L14" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
@@ -1614,7 +1619,7 @@
       <c r="S14" s="17"/>
       <c r="T14" s="17"/>
       <c r="U14" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V14" s="18"/>
       <c r="W14" s="18"/>
@@ -1624,7 +1629,7 @@
       </c>
       <c r="Z14" s="16"/>
       <c r="AA14" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB14" s="17"/>
       <c r="AC14" s="17"/>
@@ -1635,7 +1640,7 @@
       <c r="AH14" s="17"/>
       <c r="AI14" s="17"/>
       <c r="AJ14" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AK14" s="18"/>
       <c r="AL14" s="18"/>
@@ -1646,7 +1651,7 @@
       <c r="AQ14" s="18"/>
       <c r="AR14" s="18"/>
       <c r="AS14" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AT14" s="17"/>
       <c r="AU14" s="17"/>
@@ -1658,7 +1663,7 @@
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
@@ -1669,7 +1674,7 @@
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
       <c r="L15" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
@@ -1680,7 +1685,7 @@
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
       <c r="U15" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V15" s="17"/>
       <c r="W15" s="17"/>
@@ -1690,7 +1695,7 @@
       </c>
       <c r="Z15" s="16"/>
       <c r="AA15" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB15" s="17"/>
       <c r="AC15" s="17"/>
@@ -1701,7 +1706,7 @@
       <c r="AH15" s="17"/>
       <c r="AI15" s="17"/>
       <c r="AJ15" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AK15" s="18"/>
       <c r="AL15" s="18"/>
@@ -1712,7 +1717,7 @@
       <c r="AQ15" s="18"/>
       <c r="AR15" s="18"/>
       <c r="AS15" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AT15" s="18"/>
       <c r="AU15" s="18"/>
@@ -1724,7 +1729,7 @@
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
@@ -1735,7 +1740,7 @@
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
@@ -1746,7 +1751,7 @@
       <c r="S16" s="17"/>
       <c r="T16" s="17"/>
       <c r="U16" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V16" s="17"/>
       <c r="W16" s="17"/>
@@ -1756,7 +1761,7 @@
       </c>
       <c r="Z16" s="16"/>
       <c r="AA16" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB16" s="17"/>
       <c r="AC16" s="17"/>
@@ -1767,7 +1772,7 @@
       <c r="AH16" s="17"/>
       <c r="AI16" s="17"/>
       <c r="AJ16" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AK16" s="17"/>
       <c r="AL16" s="17"/>
@@ -1778,7 +1783,7 @@
       <c r="AQ16" s="17"/>
       <c r="AR16" s="17"/>
       <c r="AS16" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AT16" s="18"/>
       <c r="AU16" s="18"/>
@@ -1790,7 +1795,7 @@
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
@@ -1801,7 +1806,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
       <c r="L17" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
@@ -1812,7 +1817,7 @@
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
       <c r="U17" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V17" s="18"/>
       <c r="W17" s="18"/>
@@ -1822,7 +1827,7 @@
       </c>
       <c r="Z17" s="16"/>
       <c r="AA17" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB17" s="17"/>
       <c r="AC17" s="17"/>
@@ -1833,7 +1838,7 @@
       <c r="AH17" s="17"/>
       <c r="AI17" s="17"/>
       <c r="AJ17" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AK17" s="17"/>
       <c r="AL17" s="17"/>
@@ -1844,7 +1849,7 @@
       <c r="AQ17" s="17"/>
       <c r="AR17" s="17"/>
       <c r="AS17" s="18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AT17" s="18"/>
       <c r="AU17" s="18"/>
@@ -1856,7 +1861,7 @@
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
@@ -1867,7 +1872,7 @@
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
@@ -1878,7 +1883,7 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
       <c r="U18" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V18" s="18"/>
       <c r="W18" s="18"/>
@@ -1888,7 +1893,7 @@
       </c>
       <c r="Z18" s="16"/>
       <c r="AA18" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB18" s="17"/>
       <c r="AC18" s="17"/>
@@ -1899,7 +1904,7 @@
       <c r="AH18" s="17"/>
       <c r="AI18" s="17"/>
       <c r="AJ18" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK18" s="18"/>
       <c r="AL18" s="18"/>
@@ -1910,7 +1915,7 @@
       <c r="AQ18" s="18"/>
       <c r="AR18" s="18"/>
       <c r="AS18" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AT18" s="18"/>
       <c r="AU18" s="18"/>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
@@ -1933,7 +1938,7 @@
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
@@ -1944,7 +1949,7 @@
       <c r="S19" s="17"/>
       <c r="T19" s="17"/>
       <c r="U19" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V19" s="17"/>
       <c r="W19" s="17"/>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="Z19" s="16"/>
       <c r="AA19" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB19" s="17"/>
       <c r="AC19" s="17"/>
@@ -1965,7 +1970,7 @@
       <c r="AH19" s="17"/>
       <c r="AI19" s="17"/>
       <c r="AJ19" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK19" s="17"/>
       <c r="AL19" s="17"/>
@@ -1976,7 +1981,7 @@
       <c r="AQ19" s="17"/>
       <c r="AR19" s="17"/>
       <c r="AS19" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AT19" s="18"/>
       <c r="AU19" s="18"/>
@@ -1988,7 +1993,7 @@
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20"/>
@@ -1999,7 +2004,7 @@
       <c r="J20" s="20"/>
       <c r="K20" s="20"/>
       <c r="L20" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
@@ -2010,7 +2015,7 @@
       <c r="S20" s="20"/>
       <c r="T20" s="20"/>
       <c r="U20" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V20" s="20"/>
       <c r="W20" s="20"/>
